--- a/demo 2 (alpha)/Pb210_results/CFCS modeling data/SAR_model_summaries.xlsx
+++ b/demo 2 (alpha)/Pb210_results/CFCS modeling data/SAR_model_summaries.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.570864485138793</v>
+        <v>2.57046891738632</v>
       </c>
       <c r="D2">
-        <v>0.04624764813600265</v>
+        <v>0.04635149094822162</v>
       </c>
       <c r="E2">
-        <v>55.58908590505034</v>
+        <v>55.45601370747151</v>
       </c>
       <c r="F2">
-        <v>1.477708583003599E-28</v>
+        <v>1.571931166703372E-28</v>
       </c>
       <c r="G2">
-        <v>0.9534598841868673</v>
+        <v>0.9535097124379756</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.06735550268293651</v>
+        <v>-0.06754460391718876</v>
       </c>
       <c r="D3">
-        <v>0.002861287533058904</v>
+        <v>0.002867712165574836</v>
       </c>
       <c r="E3">
-        <v>-23.54027755152907</v>
+        <v>-23.55348096926226</v>
       </c>
       <c r="F3">
-        <v>4.657916402926496E-19</v>
+        <v>4.593393356327902E-19</v>
       </c>
       <c r="G3">
-        <v>0.9534598841868673</v>
+        <v>0.9535097124379756</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>6.125650276708487</v>
+        <v>6.193291016509459</v>
       </c>
       <c r="D4">
-        <v>0.3738810867253288</v>
+        <v>0.3789112252380045</v>
       </c>
       <c r="E4">
-        <v>16.38395333222268</v>
+        <v>16.34496579672266</v>
       </c>
       <c r="F4">
-        <v>3.292937934340875E-06</v>
+        <v>3.339431624619589E-06</v>
       </c>
       <c r="G4">
-        <v>0.9740168706873465</v>
+        <v>0.9740172634126486</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.1952096251853498</v>
+        <v>-0.1978374745758323</v>
       </c>
       <c r="D5">
-        <v>0.01202787048136943</v>
+        <v>0.01218969159691106</v>
       </c>
       <c r="E5">
-        <v>-16.2297744632119</v>
+        <v>-16.22989991198509</v>
       </c>
       <c r="F5">
-        <v>3.481327497516628E-06</v>
+        <v>3.481169195332913E-06</v>
       </c>
       <c r="G5">
-        <v>0.9740168706873465</v>
+        <v>0.9740172634126486</v>
       </c>
     </row>
   </sheetData>
